--- a/38주_대응전략_제니엘검토_0902.xlsx
+++ b/38주_대응전략_제니엘검토_0902.xlsx
@@ -85,7 +85,7 @@
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="9">
+  <fills count="10">
     <fill>
       <patternFill/>
     </fill>
@@ -117,6 +117,11 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="00FFF2CC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="00E8F1E6"/>
       </patternFill>
     </fill>
@@ -424,7 +429,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="84">
+  <cellXfs count="86">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -605,18 +610,21 @@
     <xf numFmtId="164" fontId="3" fillId="3" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="3" fillId="3" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="7" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="3" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="8" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
     <xf numFmtId="164" fontId="3" fillId="4" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment vertical="center"/>
     </xf>
@@ -638,7 +646,7 @@
     <xf numFmtId="164" fontId="3" fillId="0" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="8" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="9" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -646,19 +654,22 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="14" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="9" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
   </cellXfs>
@@ -1073,7 +1084,7 @@
     <col width="9.375" customWidth="1" style="53" min="8" max="8"/>
     <col width="65.375" customWidth="1" style="53" min="9" max="9"/>
     <col width="9.375" bestFit="1" customWidth="1" style="53" min="10" max="10"/>
-    <col width="68" customWidth="1" style="53" min="11" max="11"/>
+    <col width="70" customWidth="1" style="53" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1" ht="17.25" customHeight="1" s="53" thickBot="1"/>
@@ -1113,7 +1124,7 @@
       </c>
       <c r="K2" s="56" t="inlineStr">
         <is>
-          <t>제니엘 검토</t>
+          <t>제니엘 검토 (2026.09.02)</t>
         </is>
       </c>
     </row>
@@ -1149,7 +1160,7 @@
       <c r="J3" s="59" t="n"/>
       <c r="K3" s="59" t="n"/>
     </row>
-    <row r="4" ht="90" customHeight="1" s="53">
+    <row r="4" ht="130.5" customHeight="1" s="53">
       <c r="B4" s="2" t="inlineStr">
         <is>
           <t>세정</t>
@@ -1193,15 +1204,15 @@
       </c>
       <c r="K4" s="62" t="inlineStr">
         <is>
-          <t>조건부 가능
-① 여성 야간근로 개별 동의 필수 (근기법 §70②) — 미동의 발생 시 편성 재산정
-② 야간작업 특수건강진단 배치 전 실시 — 소요기간 확보 필요
-③ 심야·잔업수당 증가분 정산 반영 전제
-④ 업무도급 7명 전용 시 창고·로봇·세척·내용물 업무 공백 대책 필요</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="75" customHeight="1" s="53">
+          <t>조건부 가능 — 근로시간이 아니라 인원 문제
+① 주야 2조를 각 8H 소정근로로 편성하면 연장근로 미발생 → 3개월 한도(156H)와 무관
+② 실제 제약: 여성 야간근로 개별 동의(근기법 §70②) · 야간작업 특수건강진단 · 심야수당 50%
+③ 지원 7명 차출 후 원 소속 공백을 잔업으로 메우면 그때 한도 적용 — 9월 잔여 인당 창고 100H · 로봇(적재실) 101H · 내용물 69H는 여유, 세척 59H가 병목(세척실 4명 잔여 30H 미만)
+④ 반제품 박스 세척용 일용 2명은 별도 확보 필요</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="116" customHeight="1" s="53">
       <c r="B5" s="5" t="n"/>
       <c r="C5" s="6" t="n"/>
       <c r="D5" s="6" t="n"/>
@@ -1231,28 +1242,28 @@
           <t>Med</t>
         </is>
       </c>
-      <c r="K5" s="62" t="inlineStr">
-        <is>
-          <t>조건부 가능
-① 주 52시간 내 편성. 3개월 탄력근로 적용 시 취업규칙 및 근로자대표 서면합의 선행
-② 6명 확보 경로 확정 필요 (타 사업장 수배 / 염모 직구성 전용)
-③ 염모 가동 축소 범위 합의 필요</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="45" customHeight="1" s="53">
+      <c r="K5" s="64" t="inlineStr">
+        <is>
+          <t>가능
+① 순수 잔업·특근이므로 9월 잔여에 직결. 직선 24명 1,902H(인당 79H) · 염모 27명 3,712H(인당 138H, 잔여 부족 0명)로 여력 확보
+② 염모 직구성 7·5호 전용이 근로시간 관점에서도 최적 — 전 공정 중 소진율 최저
+③ 6명 확보 경로(타 사업장 수배 / 염모 전용) 확정 및 염모 가동 축소 범위 합의 필요</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="43.5" customHeight="1" s="53">
       <c r="B6" s="2" t="inlineStr">
         <is>
           <t>멀티</t>
         </is>
       </c>
-      <c r="C6" s="64" t="n">
+      <c r="C6" s="65" t="n">
         <v>310000</v>
       </c>
-      <c r="D6" s="64" t="n">
+      <c r="D6" s="65" t="n">
         <v>379000</v>
       </c>
-      <c r="E6" s="65">
+      <c r="E6" s="66">
         <f>D6-C6</f>
         <v/>
       </c>
@@ -1261,11 +1272,11 @@
           <t>1안)소용량 아웃소싱</t>
         </is>
       </c>
-      <c r="G6" s="66">
+      <c r="G6" s="67">
         <f>18*60*49.5</f>
         <v/>
       </c>
-      <c r="H6" s="66" t="n">
+      <c r="H6" s="67" t="n">
         <v>0</v>
       </c>
       <c r="I6" s="33" t="inlineStr">
@@ -1278,14 +1289,14 @@
           <t>Low</t>
         </is>
       </c>
-      <c r="K6" s="67" t="inlineStr">
+      <c r="K6" s="68" t="inlineStr">
         <is>
           <t>확인 필요
-도급계약상 재위탁(재하도급) 가능 여부 확인 선행. 계약 주체(AP / 제니엘)에 따라 품질·책임 범위가 달라짐</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="45" customHeight="1" s="53">
+도급계약상 재위탁(재하도급) 가능 여부 확인 선행. 계약 주체(AP / 제니엘)에 따라 품질·책임 범위 상이</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="101.5" customHeight="1" s="53">
       <c r="B7" s="5" t="n"/>
       <c r="C7" s="10" t="n"/>
       <c r="D7" s="10" t="n"/>
@@ -1295,11 +1306,11 @@
           <t>2안)멀티 7, 8호기 주야</t>
         </is>
       </c>
-      <c r="G7" s="68">
+      <c r="G7" s="69">
         <f>32*60*11*5</f>
         <v/>
       </c>
-      <c r="H7" s="68" t="n">
+      <c r="H7" s="69" t="n">
         <v>4</v>
       </c>
       <c r="I7" s="35" t="inlineStr">
@@ -1314,9 +1325,10 @@
       </c>
       <c r="K7" s="62" t="inlineStr">
         <is>
-          <t>조건부 가능
-세정 1안과 동일 (야간근로 동의 · 특수건강진단 · 수당 정산)
-◆ 산식 32×60×11H×5일에 7·8호기 2대 반영 여부 확인 요청</t>
+          <t>조건부 가능 — 세정 1안과 동일 구조
+① 별도 조 편성이면 근로시간 한도 무관. 야간 요건(동의·검진·수당)은 동일 적용
+② 기존 인원에 잔업으로 부가할 경우 멀티 20명 9월 잔여 1,631H(인당 82H), 잔여 50H 미만 4명(김해경 23H·이차영 41H·곽옥연 44H·김선희 46H) 제외 편성
+③ 산식 32×60×11H×5일에 7·8호기 2대 반영 여부 확인 요청</t>
         </is>
       </c>
     </row>
@@ -1326,14 +1338,14 @@
           <t>세럼</t>
         </is>
       </c>
-      <c r="C8" s="69">
+      <c r="C8" s="70">
         <f>60*49.5*60</f>
         <v/>
       </c>
-      <c r="D8" s="69" t="n">
+      <c r="D8" s="70" t="n">
         <v>187910</v>
       </c>
-      <c r="E8" s="70">
+      <c r="E8" s="71">
         <f>D8-C8</f>
         <v/>
       </c>
@@ -1354,25 +1366,25 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K8" s="71" t="inlineStr">
+      <c r="K8" s="72" t="inlineStr">
         <is>
           <t>해당 없음 — 포장재 이슈 (AP 확인 사항)</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="30" customHeight="1" s="53">
+    <row r="9" s="53">
       <c r="B9" s="12" t="inlineStr">
         <is>
           <t>리필</t>
         </is>
       </c>
-      <c r="C9" s="69" t="n">
+      <c r="C9" s="70" t="n">
         <v>40000</v>
       </c>
-      <c r="D9" s="69" t="n">
+      <c r="D9" s="70" t="n">
         <v>61228</v>
       </c>
-      <c r="E9" s="69">
+      <c r="E9" s="70">
         <f>D9-C9</f>
         <v/>
       </c>
@@ -1381,7 +1393,7 @@
           <t>소Lot 품목 아웃소싱</t>
         </is>
       </c>
-      <c r="G9" s="69" t="n">
+      <c r="G9" s="70" t="n">
         <v>21228</v>
       </c>
       <c r="H9" s="11" t="n"/>
@@ -1395,26 +1407,25 @@
           <t>Low</t>
         </is>
       </c>
-      <c r="K9" s="67" t="inlineStr">
-        <is>
-          <t>확인 필요
-멀티 1안과 동일. 품질 책임 소재 명확화 필요</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="60" customHeight="1" s="53">
+      <c r="K9" s="68" t="inlineStr">
+        <is>
+          <t>확인 필요 — 멀티 1안과 동일. 품질 책임 소재 명확화 필요</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="116" customHeight="1" s="53">
       <c r="B10" s="2" t="inlineStr">
         <is>
           <t>튜브</t>
         </is>
       </c>
-      <c r="C10" s="69" t="n">
+      <c r="C10" s="70" t="n">
         <v>1280000</v>
       </c>
-      <c r="D10" s="69" t="n">
+      <c r="D10" s="70" t="n">
         <v>1095000</v>
       </c>
-      <c r="E10" s="69">
+      <c r="E10" s="70">
         <f>D10-C10</f>
         <v/>
       </c>
@@ -1437,19 +1448,20 @@
           <t>진행예정</t>
         </is>
       </c>
-      <c r="K10" s="62" t="inlineStr">
+      <c r="K10" s="64" t="inlineStr">
         <is>
           <t>진행 가능
-단, '간접(주임) → 직접화'는 재검토 요청 — 도급 관리감독자 공백 발생. 대체 관리자 지정을 전제로만 가능
-9/14 개시 시 야간 관련 요건(동의·특수건강진단) 역산 일정 확보 필요</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="60" customHeight="1" s="53">
+① 튜브 17명 9월 잔여 1,287H(인당 76H) — 편성 여력 있음. 잔여 부족 2명(최명필 21H·김진만 24H) 제외
+② 단, '간접(주임) → 직접화'는 불가 — 도급 관리감독자 공백(적법성)에 더해 주임 3명 9월 잔여 74H(인당 25H)로 전 직책 최저, 근로시간 여력도 없음. 대체 관리자 지정 전제
+③ 9/14 개시 시 야간 요건(여성 동의 · 특수건강진단) 소요기간 역산 필요</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="72.5" customHeight="1" s="53">
       <c r="B11" s="29" t="n"/>
-      <c r="C11" s="72" t="n"/>
-      <c r="D11" s="73" t="n"/>
-      <c r="E11" s="74" t="n"/>
+      <c r="C11" s="73" t="n"/>
+      <c r="D11" s="74" t="n"/>
+      <c r="E11" s="75" t="n"/>
       <c r="F11" s="1" t="inlineStr">
         <is>
           <t>주야 맞교대 운영</t>
@@ -1467,27 +1479,28 @@
           <t>검토필요</t>
         </is>
       </c>
-      <c r="K11" s="75" t="inlineStr">
+      <c r="K11" s="76" t="inlineStr">
         <is>
           <t>재검토 요청
-원청 인력의 도급 라인 투입은 혼재작업으로 지휘명령 관계가 불분명해짐 (위장도급 판단의 핵심 징표). 라인 상주는 수용 곤란
-설비 트러블 대응은 요청·처리 절차로 분리 운영 제안</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="45" customHeight="1" s="53" thickBot="1">
+① 원청 인력의 도급 라인 투입은 혼재작업으로 지휘명령 관계가 불분명해짐 (위장도급 판단의 핵심 징표). 라인 상주는 수용 곤란
+② 설비 트러블 대응은 요청·처리 절차로 분리 운영 제안
+③ 주야 맞교대 자체는 별도 조 편성 시 근로시간 한도와 무관</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="58" customHeight="1" s="53" thickBot="1">
       <c r="B12" s="18" t="inlineStr">
         <is>
           <t>염모</t>
         </is>
       </c>
-      <c r="C12" s="76" t="inlineStr">
+      <c r="C12" s="77" t="inlineStr">
         <is>
           <t>대응가능</t>
         </is>
       </c>
-      <c r="D12" s="77" t="n"/>
-      <c r="E12" s="78" t="n"/>
+      <c r="D12" s="78" t="n"/>
+      <c r="E12" s="79" t="n"/>
       <c r="F12" s="19" t="inlineStr">
         <is>
           <t>-</t>
@@ -1505,18 +1518,19 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K12" s="79" t="inlineStr">
+      <c r="K12" s="80" t="inlineStr">
         <is>
           <t>가능
-세정 전용 시 염모 가동 축소 범위 및 직구성 아웃소싱 품질(QC) 검토 결과와 연계하여 확정</t>
+염모 27명 9월 잔여 3,712H(인당 138H)로 전 공정 최대. 세정 인력 소싱의 최적 자원.
+직구성 아웃소싱은 QC 검토 결과와 연계하여 확정</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="B13" s="43" t="n"/>
-      <c r="D13" s="80" t="n"/>
-    </row>
-    <row r="14" ht="165" customHeight="1" s="53">
+      <c r="D13" s="81" t="n"/>
+    </row>
+    <row r="14" ht="333.5" customHeight="1" s="53">
       <c r="B14" s="32" t="inlineStr">
         <is>
           <t>38주 292,960EA, Gap 수량 최대 가능 수량 +299,628EA, 최소 가능 수량 245,688EA</t>
@@ -1527,14 +1541,20 @@
           <t>표준Capa(주간)기준 준비 + 정상근무/2shift + Full근무 Capa + 전략에 따른 증가Capa</t>
         </is>
       </c>
-      <c r="K14" s="81" t="inlineStr">
-        <is>
-          <t>[제니엘 검증] AP 제시 산식으로 재계산 — 표기값과 일치
+      <c r="K14" s="82" t="inlineStr">
+        <is>
+          <t>[캐파 검증] AP 제시 산식으로 재계산 — 표기값과 일치
 · Gap 292,964 EA (세럼 9,710 제외)
 · 최대안 299,628 = 172,800 + 105,600 + 21,228  →  +6,668 / 필요 13명
 · 최소안 245,688 = 171,000 + 53,460 + 21,228  →  −47,272 / 필요 6명
 ▶ 최소안으로는 47,272 EA 미달. 09/01 제출한 충원 6명이 최소안에 해당하는 규모
-▶ 산식 확인 요청: 세정 1안(36×60×8H×5일×2)은 1일 8시간 기준. '2대 주야'가 2라인×16H이면 345,600으로 2배가 되어 Gap 충족 판정이 바뀜</t>
+▶ 산식 확인 요청: 세정 1안(36×60×8H×5일×2)은 1일 8시간 기준. '2대 주야'가 2라인×16H이면 345,600으로 2배가 되어 Gap 충족 판정이 바뀜
+[근로시간 상한] 3개월 탄력근로 현 단위기간 7·8·9월 · 한도 156H(12H/주 × 13주)
+· 7·8월 소진 인당 60H(한도의 38%) → 9월 잔여 전사 23,032H · 인당 96H
+· 9월을 8월 수준 풀 특근으로 재현하면 38명이 156H 초과 — 전사 요구 6,707H 중 5,268H(79%)만 편성 가능, 1,438H 부족
+· 초과 편중 공정: 세척실 6/14명(518H) · 주임 3/3명 · HnB 3/5명 — 이 3개는 공정 내 재배분 불가
+· 잔여 0H 4명(김영두·박태근·이세호·문석) 9월 시간외 전면 제외
+▶ 9월 토요특근은 3회(9/5·12·19, 인당 24H)까지가 권장 상한 (9/26은 추석연휴)</t>
         </is>
       </c>
     </row>
@@ -1594,55 +1614,67 @@
         </is>
       </c>
     </row>
-    <row r="26" s="53">
+    <row r="26" ht="43.5" customHeight="1" s="53">
       <c r="B26" s="45" t="inlineStr">
         <is>
           <t xml:space="preserve"> 1안) 10월 2일 정상근무 3~5일 휴식 후 6일 오픈</t>
         </is>
       </c>
-      <c r="K26" s="82" t="inlineStr">
-        <is>
-          <t>10/3(토) · 10/4(일) · 10/5(개천절 대체공휴일)</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" s="53">
+      <c r="K26" s="83" t="inlineStr">
+        <is>
+          <t>10/3(토) · 10/4(일) · 10/5(개천절 대체공휴일)
+◀ 10월 1주차 특근일(10/3)을 잠금 — 'MES 확보'와 '10월 1·2주 연속 특근'이 상충</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="29" customHeight="1" s="53">
       <c r="B27" s="45" t="inlineStr">
         <is>
           <t xml:space="preserve"> 2안) 10월 8일 정상근무 9~11일  휴식 후 12일 오픈</t>
         </is>
       </c>
-      <c r="K27" s="82" t="inlineStr">
-        <is>
-          <t>10/9(한글날) · 10/10(토) · 10/11(일)</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" s="53">
+      <c r="K27" s="83" t="inlineStr">
+        <is>
+          <t>10/9(한글날) · 10/10(토) · 10/11(일)
+◀ 10월 2주차 특근일(10/10)을 잠금 — 동일하게 상충</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="43.5" customHeight="1" s="53">
       <c r="B28" s="45" t="inlineStr">
         <is>
           <t xml:space="preserve"> 3안) 9월 23일 정상근무 9월 24~26일 </t>
         </is>
       </c>
-      <c r="K28" s="82" t="inlineStr">
-        <is>
-          <t>추석 연휴 활용 — 3개 안 중 근로시간 부담이 가장 적음  ▶ 권고</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="105" customHeight="1" s="53">
+      <c r="K28" s="84" t="inlineStr">
+        <is>
+          <t>추석 연휴(9/24~26) 활용 — 10월 토요일을 하나도 잠그지 않는 유일한 안
+▶ 제니엘 권고안</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="478.5" customHeight="1" s="53">
       <c r="B29" s="45" t="inlineStr">
         <is>
           <t>제니엘 검토 사항: ①10월 1,2주차 연속 특근 가능 여부 검토</t>
         </is>
       </c>
-      <c r="K29" s="83" t="inlineStr">
-        <is>
-          <t>[회신] 조건부 가능
-ⓐ 주 52시간 내 편성 — 3개월 탄력근로 서면합의 확인 선행
-ⓑ 휴일근로 개별 동의 — 10/3 · 10/5 · 10/9는 관공서 공휴일(유급휴일)이며, 여성 근로자는 휴일근로에도 동의 필요
-ⓒ 휴일근로 가산수당(8시간 이내 50% · 초과 100%) 증가분 정산 반영
-▶ 추석(9/24~26) 직후 10월 1·2주 연속 특근 시 3주 연속 무휴 근로 — 안전·품질 리스크 상승. 3안(9/23) 우선 검토 권고</t>
+      <c r="K29" s="85" t="inlineStr">
+        <is>
+          <t>[회신] 10월 '주 12H 연장 + 토특근 8H' — 문언 그대로는 위법, 총량은 적법 확보 가능
+① 근기법 §53의 주 12H 연장 한도에는 휴일근로가 포함된다. 따라서 '평일 12H + 토특근 8H = 주 20H'는 한도를 8H 초과 — 어떤 절차로도 이 형태로는 편성 불가
+② 10월은 유급휴일 3일(10/3 개천절 토 · 10/5 대체 · 10/9 한글날)로 평일 소정이 20일뿐이고, 1·2주 실근무 평일이 각 2일·3일이라 평일 잔업 흡수 여력이 구조적으로 없다
+[대안 — 인당 10월 총 근무시간 기준, 요구 기준선 256H]
+· ①안 220H (즉시 가능) : 토특근 8H + 평일 연장 4H = 주 12H. 절차 불필요, 요구 대비 14% 부족
+· ③안 236H (서면합의) : 토 2회를 소정근로일 편입(16H) + 연장 60H. 소정 여유 21.7H 범위 내라 11·12월 영향 없음. 요구 대비 8% 부족
+· ④안 256H (서면합의) : 토 5회 전부 소정화(40H) + 평일 연장 56H. 요구 총량을 정확히 충족하는 유일한 적법안. 대가는 소정 초과 18.3H만큼 11·12월 평일 2~3일을 비근무일로 지정하는 것(임금 손실 없음)
+▶ ③·④안은 10·11·12월 단위기간이 시작되기 전, 즉 9월 중 근로자대표 서면합의와 근무표 사전 확정이 전제(§51②)
+▶ 10~12월 확정 오더 물량을 받아야 ①/③/④ 중 선택 가능 — 물량 회신 요청
+[부대 확인]
+· 연장으로 처리하는 특근일이 유급휴일과 겹치면 휴일근로 가산(8H 이내 50% · 초과 100%) 및 여성 근로자 개별 동의 필요. 소정근로일로 편입하면 가산은 없어지나 근로자 동의가 더 무겁다
+· ◀ 상충 확정 요청: '10월 1·2주 연속 특근'과 MES 1안·2안은 양립 불가. 3안(9/23)만 양립
+· 추석(9/24~26) 직후 10월 1·2주까지 연속 특근 시 3주 연속 무휴 — 안전·품질 리스크
+· 9월과 10월은 단위기간이 달라 156H가 리셋된다. 9월 초과 38명도 10월에는 전원 편성 가능</t>
         </is>
       </c>
     </row>
